--- a/analisis_total.xlsx
+++ b/analisis_total.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,10 +431,502 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>72986227</t>
+          <t>74879114</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>73870794</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>72693065</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>71459447</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>72199158</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>71662279</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>73005973</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>75058268</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>71714445</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>74861128</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>73894001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>71074996</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>72634376</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>76069267</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>71522553</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>74355737</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>72692203</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>71522553</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>75959806</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>72531470</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>73179460</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>71767663</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>72707412</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>71459447</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>72093952</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>71343472</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>72887600</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>72334911</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>73170287</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>72992329</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>71363475</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>61287112</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>72053589</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>72337901</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>72592590</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>71672823</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>61386973</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>71365796</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>72591128</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>72991503</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>71677579</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>72983782</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
